--- a/Тест2/271.xlsx
+++ b/Тест2/271.xlsx
@@ -63,19 +63,19 @@
     <t xml:space="preserve">Krem mahsulotlari tarkibiga nimalar kirishi mumkin?</t>
   </si>
   <si>
-    <t xml:space="preserve">Ohak, gips va kvars qumi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rezina, plastmassa va sintetik tola</t>
+    <t xml:space="preserve">Ohak, gips va kvars qumi aralashmasi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rezina, plastmassa va sintetik tola aralashmasi</t>
   </si>
   <si>
     <t xml:space="preserve">Sut yog'i, qand, tuxum yoki o'simlik yog'lari</t>
   </si>
   <si>
-    <t xml:space="preserve">Metall kukuni, tuz va mineral moy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neft mahsuloti, bo'yoq va smola</t>
+    <t xml:space="preserve">Metall kukuni, tuz va mineral moy aralashmasi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neft mahsuloti, bo'yoq va smola aralashmasi</t>
   </si>
   <si>
     <t xml:space="preserve">To'g'ri javob: Sut yog'i, qand, tuxum yoki o'simlik yog'lari. Krem tarkibiga sut yog'i, qand, tuxum yoki o'simlik yog'lari kirishi mumkin va ular mikroblar uchun ozuqa manbai. Manba: Mavzu materiali (271.docx).</t>
